--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_masterGroup.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_masterGroup.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="18">
   <si>
     <t>id</t>
   </si>
@@ -1034,7 +1034,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -1180,7 +1180,7 @@
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="17.25" spans="1:5">
+    <row r="8" s="1" customFormat="1" ht="17.25" spans="1:8">
       <c r="A8" s="2">
         <v>401</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="17.25" spans="1:5">
+    <row r="9" s="1" customFormat="1" ht="17.25" spans="1:8">
       <c r="A9" s="2">
         <v>501</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="17.25" spans="1:5">
+    <row r="10" s="1" customFormat="1" ht="17.25" spans="1:8">
       <c r="A10" s="2">
         <v>601</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="17.25" spans="1:5">
+    <row r="11" s="1" customFormat="1" ht="17.25" spans="1:8">
       <c r="A11" s="2">
         <v>701</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="17.25" spans="1:5">
+    <row r="12" s="1" customFormat="1" ht="17.25" spans="1:8">
       <c r="A12" s="2">
         <v>801</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" customFormat="1" ht="17.25" spans="1:5">
+    <row r="13" customFormat="1" ht="17.25" spans="1:8">
       <c r="A13" s="2">
         <v>901</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="17.25" spans="1:5">
+    <row r="14" customFormat="1" ht="17.25" spans="1:8">
       <c r="A14" s="2">
         <v>1001</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="17.25" spans="1:5">
+    <row r="15" customFormat="1" ht="17.25" spans="1:8">
       <c r="A15" s="2">
         <v>1101</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="17.25" spans="1:5">
+    <row r="16" customFormat="1" ht="17.25" spans="1:8">
       <c r="A16" s="2">
         <v>1201</v>
       </c>
@@ -1369,16 +1369,16 @@
     </row>
     <row r="19" customFormat="1" ht="17.25" spans="1:5">
       <c r="A19" s="2">
-        <v>102</v>
+        <v>1801</v>
       </c>
       <c r="B19" s="2">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2">
         <v>1</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>17</v>
+      <c r="D19" s="2">
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>16</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="20" customFormat="1" ht="17.25" spans="1:5">
       <c r="A20" s="2">
-        <v>202</v>
+        <v>102</v>
       </c>
       <c r="B20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>17</v>
@@ -1403,27 +1403,27 @@
     </row>
     <row r="21" customFormat="1" ht="17.25" spans="1:5">
       <c r="A21" s="2">
+        <v>202</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="17.25" spans="1:5">
+      <c r="A22" s="2">
         <v>302</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="2">
         <v>3</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" ht="17.25" spans="1:5">
-      <c r="A22" s="2">
-        <v>402</v>
-      </c>
-      <c r="B22" s="2">
-        <v>4</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>17</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="23" ht="17.25" spans="1:5">
       <c r="A23" s="2">
-        <v>502</v>
+        <v>402</v>
       </c>
       <c r="B23" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="24" ht="17.25" spans="1:5">
       <c r="A24" s="2">
-        <v>602</v>
+        <v>502</v>
       </c>
       <c r="B24" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>17</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="25" ht="17.25" spans="1:5">
       <c r="A25" s="2">
-        <v>702</v>
+        <v>602</v>
       </c>
       <c r="B25" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>17</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="26" ht="17.25" spans="1:5">
       <c r="A26" s="2">
-        <v>802</v>
+        <v>702</v>
       </c>
       <c r="B26" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>17</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="27" ht="17.25" spans="1:5">
       <c r="A27" s="2">
-        <v>902</v>
+        <v>802</v>
       </c>
       <c r="B27" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>17</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="28" ht="17.25" spans="1:5">
       <c r="A28" s="2">
-        <v>1002</v>
+        <v>902</v>
       </c>
       <c r="B28" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="29" ht="17.25" spans="1:5">
       <c r="A29" s="2">
-        <v>1102</v>
+        <v>1002</v>
       </c>
       <c r="B29" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>17</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="30" ht="17.25" spans="1:5">
       <c r="A30" s="2">
-        <v>1202</v>
+        <v>1102</v>
       </c>
       <c r="B30" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="31" ht="17.25" spans="1:5">
       <c r="A31" s="2">
-        <v>1302</v>
+        <v>1202</v>
       </c>
       <c r="B31" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
@@ -1590,18 +1590,35 @@
     </row>
     <row r="32" ht="17.25" spans="1:5">
       <c r="A32" s="2">
+        <v>1302</v>
+      </c>
+      <c r="B32" s="2">
+        <v>13</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" ht="17.25" spans="1:5">
+      <c r="A33" s="2">
         <v>1402</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B33" s="2">
         <v>14</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="C33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>16</v>
       </c>
     </row>
